--- a/artfynd/A 31632-2025 artfynd.xlsx
+++ b/artfynd/A 31632-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr, Janne Johansson</t>
+          <t>Janne Johansson, Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr, Janne Johansson</t>
+          <t>Janne Johansson, Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 31632-2025 artfynd.xlsx
+++ b/artfynd/A 31632-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janne Johansson, Per Muhr</t>
+          <t>Per Muhr, Janne Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janne Johansson, Per Muhr</t>
+          <t>Per Muhr, Janne Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 31632-2025 artfynd.xlsx
+++ b/artfynd/A 31632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127119096</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127119095</v>
       </c>
       <c r="B3" t="n">
-        <v>57815</v>
+        <v>57819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127119176</v>
       </c>
       <c r="B4" t="n">
-        <v>57815</v>
+        <v>57819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31632-2025 artfynd.xlsx
+++ b/artfynd/A 31632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127119096</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127119095</v>
       </c>
       <c r="B3" t="n">
-        <v>57819</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127119176</v>
       </c>
       <c r="B4" t="n">
-        <v>57819</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31632-2025 artfynd.xlsx
+++ b/artfynd/A 31632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127119096</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127119095</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127119176</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31632-2025 artfynd.xlsx
+++ b/artfynd/A 31632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127119096</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127119095</v>
       </c>
       <c r="B3" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127119176</v>
       </c>
       <c r="B4" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31632-2025 artfynd.xlsx
+++ b/artfynd/A 31632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127119096</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>58027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr, Janne Johansson</t>
+          <t>Janne Johansson, Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -793,7 +793,7 @@
         <v>127119095</v>
       </c>
       <c r="B3" t="n">
-        <v>57830</v>
+        <v>57815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr, Janne Johansson</t>
+          <t>Janne Johansson, Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,7 +908,7 @@
         <v>127119176</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>57815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
